--- a/tests/otdev/fixtures/arch/architecture_template.xlsx
+++ b/tests/otdev/fixtures/arch/architecture_template.xlsx
@@ -10,8 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sys" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="app" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cmp" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="int" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interface" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="usr" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="project" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="project_scope" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,11 +438,6 @@
           <t>tags</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -453,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,12 +474,6 @@
           <t>tags</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -495,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,12 +510,6 @@
           <t>tags</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -537,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,26 +538,24 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>src</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>dst</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>interaction_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>tags</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -585,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,11 +593,112 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>detail_level</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>connect_level</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>item_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>change_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
